--- a/data/trans_orig/IP40A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP40A-Estudios-trans_orig.xlsx
@@ -962,7 +962,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5310</t>
+          <t>5843</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>631</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5385</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>622</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5845</t>
+          <t>5548</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>645</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5305</t>
+          <t>5132</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1976</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8194</t>
+          <t>9619</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2787</t>
+          <t>2728</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10874</t>
+          <t>10262</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2440</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9325</t>
+          <t>8681</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15346</t>
+          <t>15171</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23315</t>
+          <t>24437</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>37424</t>
+          <t>38042</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1331,12 +1331,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27061</t>
+          <t>27072</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>40294</t>
+          <t>39851</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1366,12 +1366,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>54866</t>
+          <t>54402</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>73782</t>
+          <t>73272</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1381,12 +1381,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>53,1%</t>
         </is>
       </c>
     </row>
@@ -1409,12 +1409,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20897</t>
+          <t>21134</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34230</t>
+          <t>34624</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1444,12 +1444,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12133</t>
+          <t>12234</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23998</t>
+          <t>24232</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1459,12 +1459,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1479,12 +1479,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36496</t>
+          <t>35831</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54642</t>
+          <t>54174</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1494,12 +1494,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,26%</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2907</t>
+          <t>3432</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11276</t>
+          <t>11243</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1537,12 +1537,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1557,12 +1557,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8916</t>
+          <t>9118</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1592,12 +1592,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>6471</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16852</t>
+          <t>17017</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1607,12 +1607,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,33%</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3535</t>
+          <t>3525</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4300</t>
+          <t>5088</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1705,12 +1705,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>619</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5085</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>698</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6136</t>
+          <t>6062</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>6466</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10531</t>
+          <t>9688</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -1978,12 +1978,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>531</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2013,12 +2013,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3993</t>
+          <t>3552</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13277</t>
+          <t>13331</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2028,12 +2028,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2048,12 +2048,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>5593</t>
+          <t>5608</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>15870</t>
+          <t>15539</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -2091,12 +2091,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5505</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15737</t>
+          <t>16140</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2106,12 +2106,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3359</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12342</t>
+          <t>13267</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2141,12 +2141,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2161,12 +2161,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11431</t>
+          <t>11522</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24464</t>
+          <t>24841</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -2204,12 +2204,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20041</t>
+          <t>19713</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37113</t>
+          <t>36228</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2219,12 +2219,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2239,12 +2239,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25407</t>
+          <t>26108</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>44103</t>
+          <t>44659</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2254,12 +2254,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2274,12 +2274,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>48738</t>
+          <t>49599</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>74070</t>
+          <t>73716</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2289,12 +2289,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -2317,12 +2317,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>57420</t>
+          <t>57193</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>82276</t>
+          <t>82259</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2332,12 +2332,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>67509</t>
+          <t>66377</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>94781</t>
+          <t>91786</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2367,12 +2367,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2387,12 +2387,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>131043</t>
+          <t>132149</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>165870</t>
+          <t>166124</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2402,12 +2402,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,62%</t>
         </is>
       </c>
     </row>
@@ -2430,12 +2430,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>145532</t>
+          <t>144763</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>176835</t>
+          <t>176937</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2465,12 +2465,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>127704</t>
+          <t>128475</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>159875</t>
+          <t>159973</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>280842</t>
+          <t>282860</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>327717</t>
+          <t>327224</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>44,56%</t>
         </is>
       </c>
     </row>
@@ -2543,12 +2543,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>65935</t>
+          <t>65560</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>91408</t>
+          <t>90657</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2558,12 +2558,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>65684</t>
+          <t>67467</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>91903</t>
+          <t>93211</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>137938</t>
+          <t>139169</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>175990</t>
+          <t>175355</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,88%</t>
         </is>
       </c>
     </row>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>5427</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16862</t>
+          <t>16593</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2671,12 +2671,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2691,12 +2691,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11628</t>
+          <t>11532</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25702</t>
+          <t>25652</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2706,12 +2706,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2726,12 +2726,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>19441</t>
+          <t>19286</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>36866</t>
+          <t>38323</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2741,12 +2741,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -2769,12 +2769,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>671</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6414</t>
+          <t>6564</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7803</t>
+          <t>7729</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2819,12 +2819,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2281</t>
+          <t>2755</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10853</t>
+          <t>11968</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2854,12 +2854,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>5378</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>4580</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -3112,12 +3112,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4851</t>
+          <t>4698</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14184</t>
+          <t>14186</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3831</t>
+          <t>3992</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13518</t>
+          <t>13536</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3162,12 +3162,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10560</t>
+          <t>10814</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23792</t>
+          <t>24005</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3197,12 +3197,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -3225,12 +3225,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9973</t>
+          <t>9441</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>22084</t>
+          <t>21444</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3240,12 +3240,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>11806</t>
+          <t>11471</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24701</t>
+          <t>24473</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>25017</t>
+          <t>25055</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>42367</t>
+          <t>42418</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,64%</t>
         </is>
       </c>
     </row>
@@ -3338,12 +3338,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>16815</t>
+          <t>17029</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>31144</t>
+          <t>30695</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>22946</t>
+          <t>22943</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>39360</t>
+          <t>39076</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>43540</t>
+          <t>44441</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>64858</t>
+          <t>65948</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,43%</t>
         </is>
       </c>
     </row>
@@ -3451,12 +3451,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>29615</t>
+          <t>29454</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>46508</t>
+          <t>45334</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>20929</t>
+          <t>21206</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>36147</t>
+          <t>37786</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>54406</t>
+          <t>54774</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>77816</t>
+          <t>77616</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,28%</t>
         </is>
       </c>
     </row>
@@ -3564,12 +3564,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>19947</t>
+          <t>19936</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>35673</t>
+          <t>35889</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3579,12 +3579,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3599,12 +3599,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>20704</t>
+          <t>20251</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>36154</t>
+          <t>34946</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3634,12 +3634,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>43656</t>
+          <t>42693</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>64099</t>
+          <t>65300</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>27,16%</t>
         </is>
       </c>
     </row>
@@ -3677,12 +3677,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2776</t>
+          <t>2581</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>11426</t>
+          <t>11380</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3692,12 +3692,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3518</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>13025</t>
+          <t>13918</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7611</t>
+          <t>8121</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>20264</t>
+          <t>20633</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2872</t>
+          <t>2830</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>678</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7009</t>
+          <t>7072</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>966</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>7351</t>
+          <t>8741</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4121</t>
+          <t>3531</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3972</t>
+          <t>3285</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -4133,12 +4133,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>897</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>8936</t>
+          <t>8456</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4168,12 +4168,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>628</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>6403</t>
+          <t>6118</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2833</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>11576</t>
+          <t>11841</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -4246,12 +4246,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6113</t>
+          <t>6174</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>16628</t>
+          <t>16787</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4261,12 +4261,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4281,12 +4281,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10039</t>
+          <t>9786</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>22268</t>
+          <t>22719</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>18998</t>
+          <t>18616</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>36267</t>
+          <t>35671</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -4359,12 +4359,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>18960</t>
+          <t>19514</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>36676</t>
+          <t>36074</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4374,12 +4374,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>17386</t>
+          <t>17489</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>33290</t>
+          <t>32986</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>40398</t>
+          <t>41517</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>64747</t>
+          <t>63856</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -4472,12 +4472,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>42003</t>
+          <t>41733</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>65192</t>
+          <t>65308</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4487,12 +4487,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>56257</t>
+          <t>54936</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>80732</t>
+          <t>80172</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>101673</t>
+          <t>103588</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>136308</t>
+          <t>136511</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -4585,12 +4585,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>96196</t>
+          <t>95905</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>127006</t>
+          <t>125975</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4600,12 +4600,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>96965</t>
+          <t>97230</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>127320</t>
+          <t>127759</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>202120</t>
+          <t>201645</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>246008</t>
+          <t>244254</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,95%</t>
         </is>
       </c>
     </row>
@@ -4698,12 +4698,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>201539</t>
+          <t>198937</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>240665</t>
+          <t>237181</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4713,12 +4713,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>185146</t>
+          <t>185361</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>221495</t>
+          <t>222607</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>395037</t>
+          <t>392110</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>450880</t>
+          <t>445077</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,0%</t>
         </is>
       </c>
     </row>
@@ -4811,12 +4811,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>97103</t>
+          <t>94676</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>126932</t>
+          <t>127466</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4846,12 +4846,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>90128</t>
+          <t>88639</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>120477</t>
+          <t>119186</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4881,12 +4881,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>195084</t>
+          <t>193777</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>238523</t>
+          <t>237939</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,38%</t>
         </is>
       </c>
     </row>
@@ -4924,12 +4924,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>11258</t>
+          <t>11648</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>25429</t>
+          <t>25561</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4959,12 +4959,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>17929</t>
+          <t>17489</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>34788</t>
+          <t>34186</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4994,12 +4994,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>31287</t>
+          <t>32457</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>53064</t>
+          <t>54405</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -5037,12 +5037,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>8856</t>
+          <t>8576</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>2069</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>9174</t>
+          <t>9608</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>4438</t>
+          <t>4320</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>14466</t>
+          <t>13788</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>3424</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5892,7 +5892,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3602</t>
+          <t>3319</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5927,7 +5927,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -5950,12 +5950,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>553</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5349</t>
+          <t>5592</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5965,12 +5965,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5985,12 +5985,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9583</t>
+          <t>9986</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3377</t>
+          <t>3561</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12040</t>
+          <t>12068</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,36%</t>
         </is>
       </c>
     </row>
@@ -6063,12 +6063,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4010</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11505</t>
+          <t>11945</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6078,12 +6078,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6098,12 +6098,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8230</t>
+          <t>8196</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18895</t>
+          <t>19248</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6133,12 +6133,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>14408</t>
+          <t>13672</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>27400</t>
+          <t>26703</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,15%</t>
         </is>
       </c>
     </row>
@@ -6176,12 +6176,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19418</t>
+          <t>19730</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30283</t>
+          <t>30550</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6191,12 +6191,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>64,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6211,12 +6211,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21847</t>
+          <t>21798</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34106</t>
+          <t>33924</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,89%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44471</t>
+          <t>44758</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61663</t>
+          <t>61442</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>57,86%</t>
         </is>
       </c>
     </row>
@@ -6289,12 +6289,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5841</t>
+          <t>6041</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14687</t>
+          <t>14676</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6024</t>
+          <t>5696</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16099</t>
+          <t>15793</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13660</t>
+          <t>13771</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>27435</t>
+          <t>26411</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>24,87%</t>
         </is>
       </c>
     </row>
@@ -6402,12 +6402,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7893</t>
+          <t>7737</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>583</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5535</t>
+          <t>5240</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2751</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11418</t>
+          <t>10651</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4470</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4539</t>
+          <t>4483</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -6750,7 +6750,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4078</t>
+          <t>4157</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6765,7 +6765,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6780,12 +6780,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>687</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6100</t>
+          <t>6546</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>768</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7265</t>
+          <t>7395</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6835,7 +6835,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -6858,12 +6858,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2498</t>
+          <t>2488</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9828</t>
+          <t>9887</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6878,7 +6878,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6893,12 +6893,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9583</t>
+          <t>9231</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5658</t>
+          <t>5816</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16348</t>
+          <t>16067</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -6971,12 +6971,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18630</t>
+          <t>19139</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34147</t>
+          <t>35285</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6986,12 +6986,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7006,12 +7006,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21613</t>
+          <t>21566</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39553</t>
+          <t>38304</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7021,12 +7021,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7041,12 +7041,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>43865</t>
+          <t>43952</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>66774</t>
+          <t>67785</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7056,12 +7056,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -7084,12 +7084,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>49554</t>
+          <t>49756</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>71178</t>
+          <t>71872</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7099,12 +7099,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>55278</t>
+          <t>55722</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>79461</t>
+          <t>79408</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7134,12 +7134,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>110854</t>
+          <t>108814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>144681</t>
+          <t>145078</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7169,12 +7169,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -7197,12 +7197,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>121246</t>
+          <t>122458</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>151904</t>
+          <t>152426</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>133845</t>
+          <t>134138</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>165038</t>
+          <t>166118</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7247,12 +7247,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>262714</t>
+          <t>265684</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>307865</t>
+          <t>307869</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>97327</t>
+          <t>97368</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>125991</t>
+          <t>126286</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7325,12 +7325,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>94338</t>
+          <t>94039</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>125223</t>
+          <t>123874</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7360,12 +7360,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>200763</t>
+          <t>200819</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>241503</t>
+          <t>240800</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7395,12 +7395,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,32%</t>
         </is>
       </c>
     </row>
@@ -7423,12 +7423,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15799</t>
+          <t>16237</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>30433</t>
+          <t>30314</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24953</t>
+          <t>24820</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>42211</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7473,12 +7473,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>45331</t>
+          <t>43874</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>68544</t>
+          <t>67798</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7508,12 +7508,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -7536,12 +7536,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4010</t>
+          <t>3921</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13278</t>
+          <t>12674</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7551,12 +7551,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>1456</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9324</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7586,12 +7586,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6444</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17421</t>
+          <t>18430</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7621,12 +7621,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -7771,7 +7771,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>3969</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4258</t>
+          <t>4166</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4592</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -7879,12 +7879,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>3886</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13062</t>
+          <t>13627</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5382</t>
+          <t>5592</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15346</t>
+          <t>15596</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7929,12 +7929,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>11671</t>
+          <t>11564</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>25623</t>
+          <t>25234</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7964,12 +7964,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -7992,12 +7992,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8651</t>
+          <t>8801</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19714</t>
+          <t>20157</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>13627</t>
+          <t>14629</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>27459</t>
+          <t>27519</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8042,12 +8042,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>25379</t>
+          <t>26045</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>43691</t>
+          <t>44059</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,18%</t>
         </is>
       </c>
     </row>
@@ -8105,12 +8105,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>17663</t>
+          <t>18090</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>32787</t>
+          <t>33005</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8120,12 +8120,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>20286</t>
+          <t>20660</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>35847</t>
+          <t>36087</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -8155,12 +8155,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>42053</t>
+          <t>41393</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>62935</t>
+          <t>63915</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,92%</t>
         </is>
       </c>
     </row>
@@ -8218,12 +8218,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>23086</t>
+          <t>22392</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>37989</t>
+          <t>38133</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8233,12 +8233,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>28110</t>
+          <t>28348</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>44804</t>
+          <t>45209</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8268,12 +8268,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>55804</t>
+          <t>55677</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>77944</t>
+          <t>77333</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8303,12 +8303,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,15%</t>
         </is>
       </c>
     </row>
@@ -8331,12 +8331,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>23183</t>
+          <t>24068</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>38790</t>
+          <t>39782</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8346,12 +8346,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8366,12 +8366,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>18179</t>
+          <t>17425</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>32034</t>
+          <t>32589</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8381,12 +8381,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8401,12 +8401,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>45571</t>
+          <t>45003</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>66543</t>
+          <t>66575</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8416,12 +8416,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,96%</t>
         </is>
       </c>
     </row>
@@ -8444,12 +8444,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6511</t>
+          <t>6138</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>16504</t>
+          <t>16263</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8459,12 +8459,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8479,12 +8479,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>9175</t>
+          <t>9816</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>21710</t>
+          <t>22500</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8494,12 +8494,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8514,12 +8514,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>18391</t>
+          <t>18641</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>34197</t>
+          <t>34410</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8529,12 +8529,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -8557,12 +8557,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>631</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>5938</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8572,12 +8572,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8597,7 +8597,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3185</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8612,7 +8612,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8627,12 +8627,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>7022</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8642,12 +8642,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -8710,7 +8710,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5875</t>
+          <t>4775</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8725,7 +8725,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5313</t>
+          <t>4640</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -8900,12 +8900,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>640</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>5582</t>
+          <t>5427</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8920,7 +8920,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8940,7 +8940,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4289</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>749</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6953</t>
+          <t>7105</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8990,7 +8990,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -9013,12 +9013,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>4443</t>
+          <t>4642</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>14314</t>
+          <t>15102</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9048,12 +9048,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>7238</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>18034</t>
+          <t>18476</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9063,12 +9063,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9083,12 +9083,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>13793</t>
+          <t>14031</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>29407</t>
+          <t>30111</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9098,12 +9098,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -9126,12 +9126,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>12921</t>
+          <t>12576</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>27061</t>
+          <t>26762</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9141,12 +9141,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9161,12 +9161,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>18108</t>
+          <t>17458</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>34230</t>
+          <t>34413</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9176,12 +9176,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>34131</t>
+          <t>34992</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>56290</t>
+          <t>55499</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9211,12 +9211,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -9239,12 +9239,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>40592</t>
+          <t>40751</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>62437</t>
+          <t>61818</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9254,12 +9254,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9274,12 +9274,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>46125</t>
+          <t>46273</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>70151</t>
+          <t>70543</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9289,12 +9289,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>91944</t>
+          <t>93199</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>125962</t>
+          <t>126014</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9324,12 +9324,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -9352,12 +9352,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>77985</t>
+          <t>78569</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>106561</t>
+          <t>105691</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9367,12 +9367,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9387,12 +9387,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>94111</t>
+          <t>93099</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>123676</t>
+          <t>124571</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9402,12 +9402,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>179414</t>
+          <t>179569</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>221789</t>
+          <t>223157</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9437,12 +9437,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,72%</t>
         </is>
       </c>
     </row>
@@ -9465,12 +9465,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>157338</t>
+          <t>159078</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>192822</t>
+          <t>193423</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -9480,12 +9480,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -9500,12 +9500,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>168403</t>
+          <t>167059</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>204945</t>
+          <t>202418</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -9515,12 +9515,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -9535,12 +9535,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>336395</t>
+          <t>337893</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>386624</t>
+          <t>388769</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -9550,12 +9550,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,36%</t>
         </is>
       </c>
     </row>
@@ -9578,12 +9578,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>130426</t>
+          <t>131495</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>163272</t>
+          <t>164304</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9593,12 +9593,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9613,12 +9613,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>134099</t>
+          <t>133631</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>169600</t>
+          <t>169380</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9648,12 +9648,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>275220</t>
+          <t>275038</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>321464</t>
+          <t>322625</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9663,12 +9663,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,51%</t>
         </is>
       </c>
     </row>
@@ -9691,12 +9691,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>25978</t>
+          <t>26320</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>45029</t>
+          <t>43406</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9706,12 +9706,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9726,12 +9726,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>33540</t>
+          <t>34749</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>54808</t>
+          <t>54999</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9741,12 +9741,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -9761,12 +9761,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>65303</t>
+          <t>63427</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>93595</t>
+          <t>93209</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -9776,12 +9776,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -9804,12 +9804,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>6179</t>
+          <t>5926</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>16941</t>
+          <t>17500</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -9819,12 +9819,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -9839,12 +9839,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>3735</t>
+          <t>3590</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>12490</t>
+          <t>13181</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -9854,12 +9854,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -9874,12 +9874,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>12271</t>
+          <t>11695</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>26881</t>
+          <t>25245</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -9889,12 +9889,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
